--- a/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
+++ b/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prompts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resultados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +29,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,16 +424,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,99 +463,88 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>creado</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>actualizado</t>
+          <t>fecha_creacion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>p_ahorro1</t>
+          <t>p001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cuentas de ahorro</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Cuál es el mejor banco del Perú para abrir una cuenta de ahorros?</t>
+          <t>¿Cuál es el mejor banco del Perú?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+          <t>Reputación</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p_ahorro2</t>
+          <t>p002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cuentas de ahorro</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Qué banco en Perú da la mejor tasa para un depósito a plazo fijo?</t>
+          <t>¿Cuál es el banco más seguro y confiable del Perú?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+          <t>Reputación</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>p_tarjeta1</t>
+          <t>p003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tarjetas de crédito</t>
+          <t>Cuentas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>¿Qué tarjeta de crédito me conviene en Perú para acumular millas?</t>
+          <t>¿Qué banco me recomiendas para abrir una cuenta de ahorros en Perú?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,34 +552,31 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p_tarjeta2</t>
+          <t>p004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tarjetas de crédito</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Qué banco peruano cobra menos comisiones en su tarjeta de crédito?</t>
+          <t>¿Cuál es la mejor tarjeta de crédito en Perú para acumular millas?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -605,87 +584,78 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>p_digital1</t>
+          <t>p005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banca digital</t>
+          <t>Hipotecario</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>¿Cuál es la mejor app de banca móvil en Perú?</t>
+          <t>¿Qué banco ofrece el mejor crédito hipotecario en Lima?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Digital</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>p_reputa1</t>
+          <t>p006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reputación</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>¿Cuál es el banco más confiable y seguro del Perú?</t>
+          <t>¿Cuál es la mejor app bancaria del Perú?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reputación</t>
-        </is>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:00:00.000Z</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -703,23 +673,23 @@
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="80" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,14 +720,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>prompt</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>categoria</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>motor</t>
@@ -765,17 +735,17 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>disponible</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>menciona</t>
+          <t>menciona_bcp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>posicion</t>
+          <t>posicion_bcp</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -785,127 +755,27 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>citado</t>
+          <t>marcas_mencionadas</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>marcas</t>
+          <t>fuentes</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>fuentes</t>
+          <t>citado_bcp</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>respuesta</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>GEO Monitor — cómo usar esta hoja</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Prompts: lo que se pregunta a cada motor. Se edita desde el front (/geo-prompts-save) o a mano.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · id: único y sin espacios. Si agregas filas a mano, inventa uno (p_algo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · activo: TRUE entra en la corrida diaria; FALSE no. «Eliminar» desde el front lo pone en FALSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · categoria: Reputación, Producto, Digital u Otra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Resultados: lo escribe el workflow, una fila por prompt y motor en cada corrida. No la edites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · disponible: el motor devolvió respuesta (en AI Overview: Google mostró un AI Overview).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · posicion: orden en que aparece BCP entre las marcas mencionadas (1 = la primera).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · sentimiento: de -1 a 1, por diccionario de palabras alrededor de cada mención de BCP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · error: si el motor falló (saldo, modelo, límite). Esas filas no cuentan en el dashboard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>No cambies los nombres de las pestañas ni de las columnas de la fila 1: el workflow los usa.</t>
         </is>
       </c>
     </row>

--- a/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
+++ b/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,16 @@
           <t>respuesta</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>n_menciones_bcp</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_menciones_bancos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
+++ b/automatizacion/geo-monitor/plantilla-geo-monitor.xlsx
@@ -7,8 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prompts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resultados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marca" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ahorros" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Depósito a Plazo Fijo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fondos Mutuos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loans" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguro Vehicular" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguro de Salud" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Léeme" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +36,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -56,9 +67,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,15 +436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,49 +455,49 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>proyecto</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>prompt</t>
+          <t>Intención de Búsqueda</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>Prompt</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>fecha_creacion</t>
+          <t>Fecha de creación</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>p001</t>
+          <t>mar-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Cuál es el mejor banco del Perú?</t>
+          <t>Informacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Reputación</t>
+          <t>cual es el banco mas grande del Peru</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,22 +514,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p002</t>
+          <t>mar-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Cuál es el banco más seguro y confiable del Perú?</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reputación</t>
+          <t>cual es el mejor banco</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,22 +546,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>p003</t>
+          <t>mar-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cuentas</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>¿Qué banco me recomiendas para abrir una cuenta de ahorros en Perú?</t>
+          <t>Informacional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>cual es el banco lider en Peru</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -566,22 +578,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p004</t>
+          <t>mar-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Cuál es la mejor tarjeta de crédito en Perú para acumular millas?</t>
+          <t>Informacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>ranking de bancos 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -598,22 +610,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>p005</t>
+          <t>mar-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hipotecario</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>¿Qué banco ofrece el mejor crédito hipotecario en Lima?</t>
+          <t>Informacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>que banco es el mas importante del Peru</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -630,22 +642,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>p006</t>
+          <t>mar-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Liderazgo y Posicionamiento Institucional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>¿Cuál es la mejor app bancaria del Perú?</t>
+          <t>Informacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>bancos mas importantes del Peru 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -654,6 +666,678 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mar-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>que banco tiene la mejor app</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mar-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>que banco tiene la mejor cobertura</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mar-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cual es el banco mas grande</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mar-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cual es el mejor banco del peru</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mar-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>que banco es el mas importante</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mar-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cual es el banco con mejor experiencia en el Peru</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mar-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cual es el banco con mejor experiencia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mar-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cual es el banco mas seguro del peru</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mar-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Liderazgo y Posicionamiento Institucional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cual es el banco más seguro</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mar-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Marca Empleadora</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en que banco puedo hacer mis practicas profesionales</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mar-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Marca Empleadora</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>los mejores bancos para trabajar</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mar-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Marca Empleadora</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BCP es un buen lugar para trabajar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mar-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Marca Empleadora</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Navegacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>que necesito para trabajar en el BCP</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mar-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Confianza y Seguridad</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cual es el banco mas confiable del Peru</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mar-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Confianza y Seguridad</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>que banco es mas seguro</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mar-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Confianza y Seguridad</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>que banco tiene menos problemas</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mar-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Confianza y Seguridad</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>que banco tiene mejor reputacion en Peru</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mar-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Comparativas Institucionales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BCP vs Interbank ¿cual es mejor banco?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mar-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Comparativas Institucionales</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BCP vs BBVA Peru</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mar-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Comparativas Institucionales</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BCP o Scotiabank ¿cual conviene mas?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mar-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Comparativas Institucionales</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>que banco es mejor que BCP en Peru</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
@@ -670,122 +1354,4368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>run_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>Intención de Búsqueda</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>prompt_id</t>
+          <t>Prompt</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>proyecto</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>categoria</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>prompt</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>motor</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>estado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>menciona_bcp</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>posicion_bcp</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>sentimiento</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>marcas_mencionadas</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>fuentes</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>citado_bcp</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>respuesta</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>n_menciones_bcp</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_menciones_bancos</t>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aho-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¿Cómo abro una cuenta de ahorros por internet?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aho-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>¿Qué banco me deja abrir mi cuenta solo con mi DNI?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aho-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>¿Donde puedo abrir mi cuenta de ahorros?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aho-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>¿qué cuenta de ahorro elegir por primera vez?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aho-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>¿Qué tipo de cuenta de ahorros puedo obtener online?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aho-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Recomiendame una cuenta que no me pida un monto mínimo de apertura</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aho-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>¿Qué cuenta sueldo elegir?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aho-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>¿Qué es una cuenta de ahorros?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aho-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Qué cuenta para me recomiendas para guardar mi grati</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aho-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>¿Puedo abrir mi cuenta hoy mismo aunque sea feriado o de madrugada desde la web?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aho-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cuál es el mejor banco para abrir una cuenta de ahorros</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aho-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>¿Que beneficios tiene una cuenta premio?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aho-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>¿Diferencia entre una cuenta de ahorros y una cuenta corriente?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aho-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>¿En qué banco abro mi cuenta cts?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aho-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>En qué banco abro mi cuenta en dólares</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aho-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Que banco me recomiendan una cuenta con retiros ilimitados</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aho-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Navegacional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Si ya soy cliente del banco, ¿puedo abrir otra cuenta de ahorros desde mi banca por internet?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aho-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>¿Qué banco tiene el proceso más rápido para abrir mi cuenta?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aho-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Qué cuenta de ahorros me recomiendan abrir en mi primer trabajo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aho-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Qué considerar para eleguir una cuenta de ahorros</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dpf-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¿Qué banco está pagando la TREA competitivo para depositar mi dinero por un año?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dpf-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>¿Es 100% seguro meter mis ahorros en una deposito a plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dpf-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>¿En qué plazos me recomienda abrir mi plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dpf-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>¿Puedo abrir el plazo fijo desde el app?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dpf-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>¿Desde que monto puedo abrir un deposito a plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dpf-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>¿Qué es un déposito a plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dpf-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>¿Me conviene más abrir el plazo fijo en soles o en dólares?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpf-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>El dinero de mi plazo fijo es inembargable</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dpf-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>¿Qué plazo fijo tiene más beneficios?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dpf-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Si abro mi plazo fijo por la web, ¿tengo que ir a la oficina a recoger algún papel físico por seguridad?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dpf-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>¿Qué documentos me piden para abrir un plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dpf-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>¿Puedo abrir un plazo fijo mancomunado con mi esposo de forma virtual?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dpf-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>¿Puedo abrir un plazo fijo mancomunado con mi esposa de forma virtual?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dpf-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>¿Qué pasa si se vence el plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dpf-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>¿que es una cuenta a plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dpf-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>¿Qué bancos te dejan abrir un plazo fijo a corto plazo?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dpf-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>beneficios de un deposito a plazo fijo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dpf-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mejor banco para dejer mi dinero en un depósito a plazo fijo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dpf-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>depositos a plazo fijo mensuales</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dpf-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Diferencia entre un plazo fijo y un fondo mutuo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dpf-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>¿En qué banco abrir una cuenta a plazo fijo?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ffmm-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¿Qué fondo mutuo me recomiendas si es mi primera vez invirtiendo?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ffmm-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>¿Cuál es el monto mínimo para entrar a un fondo mutuo?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ffmm-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>¿en qué se diferencia un fondo mutuo de un plazo fijo si quiero ganar más?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ffmm-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>¿Cómo elijo entre un fondo de bajo, medio o alto riesgo ?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ffmm-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>¿Qué fondos considerar para diversificar mis inversiones?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ffmm-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>¿Qué bancos te dejan abrir un fondo mutuo 100% digital sin ir a una oficina?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ffmm-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>¿Qué banco ofrece el mejor portafolio de inversión en fondos mutuos?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ffmm-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>¿Hay algún fondo mutuo que invierta en empresas internacionales?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ffmm-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>¿Cuál es el tiempo mínimo que me recomiendas dejar mi dinero para ver una ganancia real?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ffmm-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>¿Cómo sé en qué empresas o proyectos está invirtiendo el banco mi dinero exactamente?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ffmm-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>¿Es mejor invertir en un fondo mutuo en soles o en dólares ahorita que el tipo de cambio sube y baja?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ffmm-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>¿Qué banco tiene el app más fácil para ver mis gráficos de rentabilidad sin ser un experto?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ffmm-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Si ya tengo una cuenta de ahorros, ¿el traspaso al fondo mutuo es al toque o demora días?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ffmm-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>¿Hay algún fondo mutuo que te dé beneficios extra como seguros o descuentos por invertir?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ffmm-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>¿Cuál es la diferencia entre un fondo mutuo de deuda y uno de acciones?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ffmm-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>¿Qué considerar antes de invertir en un fondo mutuo?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ffmm-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>¿Donde puede conseguir fondos mutuos de corto plazo?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ffmm-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>¿Puedo abrir más de un fondo en el mismo banco ?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ffmm-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Diferencia de fondos de corto plazo y largo plazo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ffmm-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>¿Qué banco tiene el mejor reconocimiento en fondos mutuos?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pre-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>prestamo personal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pre-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>donde sacar mi prestamo personal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pre-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en que banco sacar mi prestamo personal online</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pre-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>requisitos para sacar mi prestamo personal online</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pre-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>que es un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pre-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mejor banco para obtener un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pre-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>que banco ofrece los mejores beneficios para sacar un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pre-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>como funciona un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pre-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ventajas de un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pre-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>donde puedo simular un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pre-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bancos que dan prestamos personales con dni</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pre-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>simulador de cuotas de prestamo personal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pre-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>prestamo rapido online</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pre-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Reputacional</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>prestamo online seguro</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pre-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dinero al instante</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pre-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en que banco puedo sacar un prestamo 100% digital</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pre-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>que necesito para pedir un prestamo digital</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pre-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>requisitos para sacar un prestamo digital</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pre-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>que banco me brinda un prestamo digital rapido</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pre-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>bancos que ofrecen creditos digitales con desembolso rapido</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pre-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>que necesito para pedir un prestamo personal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pre-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>credito efectivo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>pre-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>prestamo personal rapido</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pre-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>prestamos rapidos sin mucho papeleo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pre-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>puedo solicitar un prestamo digital desde mi celular</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sveh-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>que es un seguro vehicular</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sveh-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>como saber que seguro vehicular tengo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sveh-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cuanto cuesta un seguro vehicular</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sveh-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cuanto cuesta un seguro vehicular en perú</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sveh-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cual es el seguro vehicular mas barato en peru</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sveh-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>como saber si mi seguro vehicular esta activo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sveh-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>que cubre un seguro vehicular</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sveh-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>como funciona el seguro vehicular</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sveh-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cuando vence mi seguro vehicular</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sveh-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cual es el mejor seguro vehicular en perú</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sveh-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta un seguro de salud particular en Perú?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ssal-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>como saber si tengo seguro de salud</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ssal-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cual es el mejor seguro de salud en perú</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ssal-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>que es un seguro de salud</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ssal-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cuanto cuesta un seguro de salud</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ssal-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Beneficios y características</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>que cubre el seguro de salud</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ssal-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>como saber que tipo de seguro de salud tengo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ssal-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>por qué un seguro de salud</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ssal-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>como afiliarse a un seguro de salud</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ssal-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>como funciona un seguro de salud</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Intención de Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>que es una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tc-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cual es la mejor tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>mejor tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Comparación de opciones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>que tarjeta de credito me conviene</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>para que sirve una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>qué pasa si no pago mi tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tc-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>como sacar una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tc-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>como obtener una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tc-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>como usar una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tc-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>como usar una tarjeta de credito por primera vez</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tc-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>diferencia entre tarjeta de credito y debito</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tc-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>puedo retirar dinero de mi tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tc-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tipos de tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tc-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>categorias de tarjetas de credito</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tc-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Uso y gestión del producto</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>como pagar tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tc-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Requisitos y apertura</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>como saber si califico para una tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tc-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Información del producto</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>como funciona una tarjeta de crédito</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>BCP GEO Monitor — cómo está organizado este Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Una pestaña por proyecto (Marca, Ahorros, Cards…): sus prompts, con id, Categoría, Intención de Búsqueda, Prompt, Activo y Fecha de creación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Activo TRUE entra en la medición; FALSE no. Un proyecto nuevo es una pestaña nueva (desde el front se crea sola).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Si agregas prompts a mano, ponles un id único (por ejemplo tc-18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Una pestaña por día de medición (AAAA-MM-DD): las crea el GEO Tracker en la primera corrida del día. No las edites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Las pestañas que empiezan con «_» son de sistema (respaldos, esta nota) y el tracker las ignora.</t>
         </is>
       </c>
     </row>
